--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI)cn.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="31">
   <si>
     <t>CCI</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -159,14 +159,6 @@
   <si>
     <t>年化收益率</t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>深创100ETF</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>PE</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>最高价</t>
@@ -609,7 +601,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -789,6 +781,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -798,7 +793,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -977,6 +972,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -1020,7 +1018,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1200,6 +1198,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1209,7 +1210,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1389,6 +1390,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1978849.1612350328</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2022104.2217609019</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1431,7 +1435,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1611,6 +1615,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1620,7 +1627,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1800,6 +1807,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>820356.13175280904</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>863611.19227867806</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1821,11 +1831,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="375147520"/>
-        <c:axId val="401486592"/>
+        <c:axId val="436508544"/>
+        <c:axId val="436514816"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="375147520"/>
+        <c:axId val="436508544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1868,14 +1878,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401486592"/>
+        <c:crossAx val="436514816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="401486592"/>
+        <c:axId val="436514816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1926,7 +1936,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="375147520"/>
+        <c:crossAx val="436508544"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2117,7 +2127,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2297,6 +2307,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-273879.41101316386</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-703792.54386857653</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2311,8 +2324,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="472415232"/>
-        <c:axId val="472413696"/>
+        <c:axId val="538965120"/>
+        <c:axId val="538951040"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2337,7 +2350,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2517,6 +2530,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2526,7 +2542,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2706,6 +2722,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2722,11 +2741,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="472406272"/>
-        <c:axId val="472412160"/>
+        <c:axId val="538947968"/>
+        <c:axId val="538949504"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="472406272"/>
+        <c:axId val="538947968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2769,14 +2788,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472412160"/>
+        <c:crossAx val="538949504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="472412160"/>
+        <c:axId val="538949504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2827,12 +2846,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472406272"/>
+        <c:crossAx val="538947968"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="472413696"/>
+        <c:axId val="538951040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2869,12 +2888,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472415232"/>
+        <c:crossAx val="538965120"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="472415232"/>
+        <c:axId val="538965120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2883,7 +2902,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="472413696"/>
+        <c:crossAx val="538951040"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3045,7 +3064,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3225,6 +3244,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-36057.366675283578</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-60139.263576626639</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3239,8 +3261,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="427095552"/>
-        <c:axId val="427094016"/>
+        <c:axId val="460890496"/>
+        <c:axId val="460413952"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3265,7 +3287,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3445,6 +3467,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3454,7 +3479,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3634,6 +3659,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3650,11 +3678,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="401518976"/>
-        <c:axId val="401520512"/>
+        <c:axId val="460400896"/>
+        <c:axId val="460407552"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="401518976"/>
+        <c:axId val="460400896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3697,14 +3725,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401520512"/>
+        <c:crossAx val="460407552"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="401520512"/>
+        <c:axId val="460407552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3755,12 +3783,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401518976"/>
+        <c:crossAx val="460400896"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="427094016"/>
+        <c:axId val="460413952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3797,12 +3825,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427095552"/>
+        <c:crossAx val="460890496"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="427095552"/>
+        <c:axId val="460890496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3811,7 +3839,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="427094016"/>
+        <c:crossAx val="460413952"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3990,7 +4018,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4170,6 +4198,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4179,7 +4210,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4358,6 +4389,9 @@
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>1222236.9259249454</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
               </c:numCache>
@@ -4401,7 +4435,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4581,6 +4615,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4590,7 +4627,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4770,6 +4807,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>2097331.2663571048</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2142805.2789050131</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4812,7 +4852,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4992,6 +5032,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5001,7 +5044,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5181,6 +5224,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>875094.34043215937</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>920568.35298006772</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5202,11 +5248,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="438244480"/>
-        <c:axId val="438921088"/>
+        <c:axId val="504480128"/>
+        <c:axId val="504482048"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="438244480"/>
+        <c:axId val="504480128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5249,14 +5295,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="438921088"/>
+        <c:crossAx val="504482048"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="438921088"/>
+        <c:axId val="504482048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5307,7 +5353,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="438244480"/>
+        <c:crossAx val="504480128"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5498,7 +5544,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5678,6 +5724,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-43268.840010340289</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-72167.11629195197</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5692,8 +5741,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="548006912"/>
-        <c:axId val="548005376"/>
+        <c:axId val="538613248"/>
+        <c:axId val="538611712"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5718,7 +5767,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5898,6 +5947,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5907,7 +5959,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -6087,6 +6139,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6103,11 +6158,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="547804672"/>
-        <c:axId val="547806592"/>
+        <c:axId val="521980544"/>
+        <c:axId val="529949440"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="547804672"/>
+        <c:axId val="521980544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6150,14 +6205,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="547806592"/>
+        <c:crossAx val="529949440"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="547806592"/>
+        <c:axId val="529949440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6208,12 +6263,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="547804672"/>
+        <c:crossAx val="521980544"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="548005376"/>
+        <c:axId val="538611712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6250,12 +6305,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="548006912"/>
+        <c:crossAx val="538613248"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="548006912"/>
+        <c:axId val="538613248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6264,7 +6319,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="548005376"/>
+        <c:crossAx val="538611712"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6443,7 +6498,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6623,6 +6678,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6632,7 +6690,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6811,6 +6869,9 @@
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>1226222.9374500697</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
               </c:numCache>
@@ -6854,7 +6915,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7034,6 +7095,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7043,7 +7107,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7223,6 +7287,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>2098477.6097613247</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2144300.0487286719</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7265,7 +7332,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7445,6 +7512,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7454,7 +7524,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7634,6 +7704,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>872254.67231125501</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>918077.11127860215</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7655,11 +7728,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="556909696"/>
-        <c:axId val="556911232"/>
+        <c:axId val="538806912"/>
+        <c:axId val="538808704"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="556909696"/>
+        <c:axId val="538806912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7702,14 +7775,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556911232"/>
+        <c:crossAx val="538808704"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="556911232"/>
+        <c:axId val="538808704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7760,7 +7833,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556909696"/>
+        <c:crossAx val="538806912"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7951,7 +8024,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8131,6 +8204,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-43268.840010340289</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-60139.263576626639</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8145,8 +8221,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="656609280"/>
-        <c:axId val="654231424"/>
+        <c:axId val="571987840"/>
+        <c:axId val="571985920"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8171,7 +8247,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8351,6 +8427,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8360,7 +8439,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8540,6 +8619,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8556,11 +8638,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="654091776"/>
-        <c:axId val="654229888"/>
+        <c:axId val="539340800"/>
+        <c:axId val="539342720"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="654091776"/>
+        <c:axId val="539340800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8603,14 +8685,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="654229888"/>
+        <c:crossAx val="539342720"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="654229888"/>
+        <c:axId val="539342720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8661,12 +8743,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="654091776"/>
+        <c:crossAx val="539340800"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="654231424"/>
+        <c:axId val="571985920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8703,12 +8785,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="656609280"/>
+        <c:crossAx val="571987840"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="656609280"/>
+        <c:axId val="571987840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8717,7 +8799,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="654231424"/>
+        <c:crossAx val="571985920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8896,7 +8978,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9076,6 +9158,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9085,7 +9170,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9264,6 +9349,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -9307,7 +9395,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9487,6 +9575,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9496,7 +9587,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9676,6 +9767,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>17567754.333578344</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>17963358.223627001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9718,7 +9812,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9898,6 +9992,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9907,7 +10004,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10087,6 +10184,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>7604968.9543284345</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>8000572.8443770912</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10108,11 +10208,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="656642048"/>
-        <c:axId val="656644352"/>
+        <c:axId val="573801216"/>
+        <c:axId val="573838464"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="656642048"/>
+        <c:axId val="573801216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10155,14 +10255,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="656644352"/>
+        <c:crossAx val="573838464"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="656644352"/>
+        <c:axId val="573838464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10213,7 +10313,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="656642048"/>
+        <c:crossAx val="573801216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10404,7 +10504,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10584,6 +10684,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>12761408.348849542</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>12043831.475181028</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10598,8 +10701,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="657036032"/>
-        <c:axId val="656931456"/>
+        <c:axId val="584578560"/>
+        <c:axId val="579984000"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10624,7 +10727,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10804,6 +10907,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10813,7 +10919,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10993,6 +11099,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11009,11 +11118,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="656660352"/>
-        <c:axId val="656661888"/>
+        <c:axId val="579843584"/>
+        <c:axId val="579981312"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="656660352"/>
+        <c:axId val="579843584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11056,14 +11165,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="656661888"/>
+        <c:crossAx val="579981312"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="656661888"/>
+        <c:axId val="579981312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11114,12 +11223,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="656660352"/>
+        <c:crossAx val="579843584"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="656931456"/>
+        <c:axId val="579984000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11156,12 +11265,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="657036032"/>
+        <c:crossAx val="584578560"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="657036032"/>
+        <c:axId val="584578560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11170,7 +11279,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="656931456"/>
+        <c:crossAx val="579984000"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11349,7 +11458,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11529,6 +11638,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11538,7 +11650,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11717,6 +11829,9 @@
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>8864712.2860347666</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
               </c:numCache>
@@ -11760,7 +11875,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11940,6 +12055,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11949,7 +12067,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12129,6 +12247,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>16990140.268494405</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>17388332.741541885</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12171,7 +12292,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12351,6 +12472,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12360,7 +12484,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12540,6 +12664,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>8125427.9824596383</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>8523620.4555071183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12561,11 +12688,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="472308352"/>
-        <c:axId val="472387968"/>
+        <c:axId val="538919680"/>
+        <c:axId val="538921216"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="472308352"/>
+        <c:axId val="538919680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12608,14 +12735,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472387968"/>
+        <c:crossAx val="538921216"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="472387968"/>
+        <c:axId val="538921216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12666,7 +12793,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472308352"/>
+        <c:crossAx val="538919680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13380,7 +13507,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -16023,6 +16150,44 @@
         <v>241671.12627942342</v>
       </c>
     </row>
+    <row r="63" spans="1:12" ht="12.75">
+      <c r="A63" s="12">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="13">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="13">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="14">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="14">
+        <v>-60139.263576626639</v>
+      </c>
+      <c r="F63" s="15">
+        <v>-47131.083462289775</v>
+      </c>
+      <c r="G63" s="15">
+        <v>1348192.6340495073</v>
+      </c>
+      <c r="H63" s="15">
+        <v>1720293.8319048518</v>
+      </c>
+      <c r="I63" s="15">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J63" s="15">
+        <v>2022104.2217609019</v>
+      </c>
+      <c r="K63" s="15">
+        <v>863611.19227867806</v>
+      </c>
+      <c r="L63" s="14">
+        <v>301810.38985605008</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -16039,7 +16204,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM62"/>
+  <dimension ref="A1:AM63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -16074,13 +16239,13 @@
   <sheetData>
     <row r="1" spans="1:39" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -16110,10 +16275,10 @@
         <v>18</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>4</v>
@@ -16134,7 +16299,7 @@
         <v>3</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:39" ht="14.1" customHeight="1">
@@ -20133,6 +20298,71 @@
         <v>128.75846332158676</v>
       </c>
       <c r="U62" s="11">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" ht="12.75">
+      <c r="A63" s="12">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="13">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="13">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="14">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="14">
+        <v>-72167.11629195197</v>
+      </c>
+      <c r="F63" s="15">
+        <v>-56557.300154747725</v>
+      </c>
+      <c r="G63" s="15">
+        <v>1410345.4730035041</v>
+      </c>
+      <c r="H63" s="15">
+        <v>1799600.8558327174</v>
+      </c>
+      <c r="I63" s="15">
+        <v>1222236.9259249454</v>
+      </c>
+      <c r="J63" s="15">
+        <v>2142805.2789050131</v>
+      </c>
+      <c r="K63" s="15">
+        <v>920568.35298006772</v>
+      </c>
+      <c r="L63" s="14">
+        <v>343204.42307229573</v>
+      </c>
+      <c r="M63" s="23">
+        <v>1.2970000505447388</v>
+      </c>
+      <c r="N63" s="23">
+        <v>1.1710000038146973</v>
+      </c>
+      <c r="O63" s="23">
+        <v>1.2480000257492065</v>
+      </c>
+      <c r="P63" s="23">
+        <v>1.0304285770370849</v>
+      </c>
+      <c r="Q63" s="23">
+        <v>0.21757144871212164</v>
+      </c>
+      <c r="R63" s="23">
+        <v>0.10519728409189744</v>
+      </c>
+      <c r="S63" s="9">
+        <v>1.5779592613784615E-3</v>
+      </c>
+      <c r="T63" s="9">
+        <v>137.88153727242442</v>
+      </c>
+      <c r="U63" s="11">
         <v>1.2</v>
       </c>
     </row>
@@ -20152,7 +20382,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -20226,7 +20456,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -23142,6 +23372,50 @@
       </c>
       <c r="N62" s="9">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="12.75">
+      <c r="A63" s="12">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="13">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="13">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="14">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="14">
+        <v>-60139.263576626639</v>
+      </c>
+      <c r="F63" s="15">
+        <v>-47131.083462289775</v>
+      </c>
+      <c r="G63" s="15">
+        <v>1431011.2450437082</v>
+      </c>
+      <c r="H63" s="15">
+        <v>1825970.3814290198</v>
+      </c>
+      <c r="I63" s="15">
+        <v>1226222.9374500697</v>
+      </c>
+      <c r="J63" s="15">
+        <v>2144300.0487286719</v>
+      </c>
+      <c r="K63" s="15">
+        <v>918077.11127860215</v>
+      </c>
+      <c r="L63" s="14">
+        <v>318329.66729965212</v>
+      </c>
+      <c r="M63" s="9">
+        <v>66.335527216233743</v>
+      </c>
+      <c r="N63" s="9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -23160,7 +23434,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -23198,10 +23472,10 @@
         <v>19</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -23234,7 +23508,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -26150,6 +26424,50 @@
       </c>
       <c r="N62" s="9">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="12.75">
+      <c r="A63" s="12">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="13">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="13">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="14">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="14">
+        <v>-915628.10722505616</v>
+      </c>
+      <c r="F63" s="15">
+        <v>-717576.87366851489</v>
+      </c>
+      <c r="G63" s="15">
+        <v>12043831.475181028</v>
+      </c>
+      <c r="H63" s="15">
+        <v>15367929.237992419</v>
+      </c>
+      <c r="I63" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J63" s="15">
+        <v>17963358.223627001</v>
+      </c>
+      <c r="K63" s="15">
+        <v>8000572.8443770912</v>
+      </c>
+      <c r="L63" s="14">
+        <v>2595428.9856345826</v>
+      </c>
+      <c r="M63" s="9">
+        <v>66.335527216233743</v>
+      </c>
+      <c r="N63" s="9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -26168,7 +26486,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI62"/>
+  <dimension ref="A1:AI63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -26206,19 +26524,19 @@
         <v>19</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>11</v>
@@ -26248,7 +26566,7 @@
         <v>0</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="14.1" customHeight="1">
@@ -29526,6 +29844,56 @@
       </c>
       <c r="P62" s="9">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="12.75">
+      <c r="A63" s="12">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="13">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="13">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="14">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="14">
+        <v>3094800</v>
+      </c>
+      <c r="F63" s="14">
+        <v>4026308.4497372219</v>
+      </c>
+      <c r="G63" s="14">
+        <v>-703792.54386857653</v>
+      </c>
+      <c r="H63" s="15">
+        <v>-551561.54486233124</v>
+      </c>
+      <c r="I63" s="15">
+        <v>12293349.432560524</v>
+      </c>
+      <c r="J63" s="15">
+        <v>15686314.157319667</v>
+      </c>
+      <c r="K63" s="15">
+        <v>8864712.2860347666</v>
+      </c>
+      <c r="L63" s="15">
+        <v>17388332.741541885</v>
+      </c>
+      <c r="M63" s="15">
+        <v>8523620.4555071183</v>
+      </c>
+      <c r="N63" s="14">
+        <v>1702018.5842222178</v>
+      </c>
+      <c r="O63" s="9">
+        <v>66.335527216233743</v>
+      </c>
+      <c r="P63" s="9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI)cn.xlsx
@@ -133,10 +133,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -158,6 +154,10 @@
   </si>
   <si>
     <t>年化收益率</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -601,7 +601,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -784,6 +784,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -793,7 +796,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -975,6 +978,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -1018,7 +1024,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1201,6 +1207,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1210,7 +1219,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1393,6 +1402,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>2022104.2217609019</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1794259.6267486978</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1435,7 +1447,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1618,6 +1630,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1627,7 +1642,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1810,6 +1825,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>863611.19227867806</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>635766.59726647404</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1831,11 +1849,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="436508544"/>
-        <c:axId val="436514816"/>
+        <c:axId val="503908608"/>
+        <c:axId val="503914496"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="436508544"/>
+        <c:axId val="503908608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1878,14 +1896,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="436514816"/>
+        <c:crossAx val="503914496"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="436514816"/>
+        <c:axId val="503914496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1936,7 +1954,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="436508544"/>
+        <c:crossAx val="503908608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2127,7 +2145,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2310,6 +2328,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-703792.54386857653</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-351576.30531150417</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2324,8 +2345,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="538965120"/>
-        <c:axId val="538951040"/>
+        <c:axId val="692910720"/>
+        <c:axId val="692909184"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2350,7 +2371,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2533,6 +2554,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2542,7 +2566,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2725,6 +2749,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2741,11 +2768,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="538947968"/>
-        <c:axId val="538949504"/>
+        <c:axId val="692893568"/>
+        <c:axId val="692895104"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="538947968"/>
+        <c:axId val="692893568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2788,14 +2815,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="538949504"/>
+        <c:crossAx val="692895104"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="538949504"/>
+        <c:axId val="692895104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2846,12 +2873,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="538947968"/>
+        <c:crossAx val="692893568"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="538951040"/>
+        <c:axId val="692909184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2888,12 +2915,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="538965120"/>
+        <c:crossAx val="692910720"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="538965120"/>
+        <c:axId val="692910720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2902,7 +2929,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="538951040"/>
+        <c:crossAx val="692909184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3064,7 +3091,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3247,6 +3274,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-60139.263576626639</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-35250.090060671617</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3261,8 +3291,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="460890496"/>
-        <c:axId val="460413952"/>
+        <c:axId val="509547264"/>
+        <c:axId val="503970432"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3287,7 +3317,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3470,6 +3500,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3479,7 +3512,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3662,6 +3695,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3678,11 +3714,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="460400896"/>
-        <c:axId val="460407552"/>
+        <c:axId val="503966336"/>
+        <c:axId val="503968896"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="460400896"/>
+        <c:axId val="503966336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3725,14 +3761,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="460407552"/>
+        <c:crossAx val="503968896"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="460407552"/>
+        <c:axId val="503968896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3783,12 +3819,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="460400896"/>
+        <c:crossAx val="503966336"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="460413952"/>
+        <c:axId val="503970432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3825,12 +3861,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="460890496"/>
+        <c:crossAx val="509547264"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="460890496"/>
+        <c:axId val="509547264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3839,7 +3875,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="460413952"/>
+        <c:crossAx val="503970432"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4018,7 +4054,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4201,6 +4237,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4210,7 +4249,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4392,6 +4431,9 @@
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>1222236.9259249454</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
               </c:numCache>
@@ -4435,7 +4477,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4618,6 +4660,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4627,7 +4672,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4810,6 +4855,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>2142805.2789050131</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1904456.8522721031</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4852,7 +4900,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5035,6 +5083,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5044,7 +5095,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5227,6 +5278,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>920568.35298006772</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>682219.92634715769</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5248,11 +5302,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="504480128"/>
-        <c:axId val="504482048"/>
+        <c:axId val="569178752"/>
+        <c:axId val="692671232"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="504480128"/>
+        <c:axId val="569178752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5295,14 +5349,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="504482048"/>
+        <c:crossAx val="692671232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="504482048"/>
+        <c:axId val="692671232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5353,7 +5407,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="504480128"/>
+        <c:crossAx val="569178752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5544,7 +5598,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5727,6 +5781,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-72167.11629195197</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-35250.090060671617</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5741,8 +5798,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="538613248"/>
-        <c:axId val="538611712"/>
+        <c:axId val="693161984"/>
+        <c:axId val="692967680"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5767,7 +5824,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5950,6 +6007,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5959,7 +6019,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -6142,6 +6202,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6158,11 +6221,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="521980544"/>
-        <c:axId val="529949440"/>
+        <c:axId val="692865664"/>
+        <c:axId val="692965760"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="521980544"/>
+        <c:axId val="692865664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6205,14 +6268,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529949440"/>
+        <c:crossAx val="692965760"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="529949440"/>
+        <c:axId val="692965760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6263,12 +6326,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="521980544"/>
+        <c:crossAx val="692865664"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="538611712"/>
+        <c:axId val="692967680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6305,12 +6368,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="538613248"/>
+        <c:crossAx val="693161984"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="538613248"/>
+        <c:axId val="693161984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6319,7 +6382,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="538611712"/>
+        <c:crossAx val="692967680"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6498,7 +6561,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6681,6 +6744,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6690,7 +6756,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6872,6 +6938,9 @@
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>1226222.9374500697</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
               </c:numCache>
@@ -6915,7 +6984,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7098,6 +7167,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7107,7 +7179,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7290,6 +7362,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>2144300.0487286719</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1902459.1060100065</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7332,7 +7407,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7515,6 +7590,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7524,7 +7602,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7707,6 +7785,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>918077.11127860215</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>676236.16855993681</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7728,11 +7809,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="538806912"/>
-        <c:axId val="538808704"/>
+        <c:axId val="728949888"/>
+        <c:axId val="728952832"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="538806912"/>
+        <c:axId val="728949888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7775,14 +7856,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="538808704"/>
+        <c:crossAx val="728952832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="538808704"/>
+        <c:axId val="728952832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7833,7 +7914,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="538806912"/>
+        <c:crossAx val="728949888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8024,7 +8105,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8207,6 +8288,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-60139.263576626639</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-35250.090060671617</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8221,8 +8305,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="571987840"/>
-        <c:axId val="571985920"/>
+        <c:axId val="730074496"/>
+        <c:axId val="730072192"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8247,7 +8331,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8430,6 +8514,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8439,7 +8526,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8622,6 +8709,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8638,11 +8728,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="539340800"/>
-        <c:axId val="539342720"/>
+        <c:axId val="730031616"/>
+        <c:axId val="730033536"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="539340800"/>
+        <c:axId val="730031616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8685,14 +8775,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="539342720"/>
+        <c:crossAx val="730033536"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="539342720"/>
+        <c:axId val="730033536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8743,12 +8833,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="539340800"/>
+        <c:crossAx val="730031616"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="571985920"/>
+        <c:axId val="730072192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8785,12 +8875,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="571987840"/>
+        <c:crossAx val="730074496"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="571987840"/>
+        <c:axId val="730074496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8799,7 +8889,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="571985920"/>
+        <c:crossAx val="730072192"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8978,7 +9068,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9161,6 +9251,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9170,7 +9263,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9352,6 +9445,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -9395,7 +9491,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9578,6 +9674,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9587,7 +9686,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9770,6 +9869,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>17963358.223627001</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>15927950.34825873</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9812,7 +9914,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9995,6 +10097,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10004,7 +10109,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10187,6 +10292,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>8000572.8443770912</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5965164.9690088201</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10208,11 +10316,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="573801216"/>
-        <c:axId val="573838464"/>
+        <c:axId val="730145152"/>
+        <c:axId val="730147840"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="573801216"/>
+        <c:axId val="730145152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10255,14 +10363,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="573838464"/>
+        <c:crossAx val="730147840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="573838464"/>
+        <c:axId val="730147840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10313,7 +10421,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="573801216"/>
+        <c:crossAx val="730145152"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10504,7 +10612,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10687,6 +10795,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>12043831.475181028</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>11759663.097474437</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10701,8 +10812,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="584578560"/>
-        <c:axId val="579984000"/>
+        <c:axId val="692485120"/>
+        <c:axId val="692483584"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10727,7 +10838,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10910,6 +11021,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10919,7 +11033,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -11102,6 +11216,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11118,11 +11235,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="579843584"/>
-        <c:axId val="579981312"/>
+        <c:axId val="691517696"/>
+        <c:axId val="692482048"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="579843584"/>
+        <c:axId val="691517696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11165,14 +11282,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="579981312"/>
+        <c:crossAx val="692482048"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="579981312"/>
+        <c:axId val="692482048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11223,12 +11340,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="579843584"/>
+        <c:crossAx val="691517696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="579984000"/>
+        <c:axId val="692483584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11265,12 +11382,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="584578560"/>
+        <c:crossAx val="692485120"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="584578560"/>
+        <c:axId val="692485120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11279,7 +11396,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="579984000"/>
+        <c:crossAx val="692483584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11458,7 +11575,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11641,6 +11758,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11650,7 +11770,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11832,6 +11952,9 @@
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>8864712.2860347666</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
               </c:numCache>
@@ -11875,7 +11998,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12058,6 +12181,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12067,7 +12193,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12250,6 +12376,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>17388332.741541885</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>15310756.323999755</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12292,7 +12421,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12475,6 +12604,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12484,7 +12616,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12667,6 +12799,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>8523620.4555071183</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>6446044.0379649885</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12688,11 +12823,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="538919680"/>
-        <c:axId val="538921216"/>
+        <c:axId val="692680960"/>
+        <c:axId val="692707328"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="538919680"/>
+        <c:axId val="692680960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12735,14 +12870,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="538921216"/>
+        <c:crossAx val="692707328"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="538921216"/>
+        <c:axId val="692707328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12793,7 +12928,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="538919680"/>
+        <c:crossAx val="692680960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13507,7 +13642,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG63"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -13638,28 +13773,28 @@
       </c>
       <c r="M3" s="9"/>
       <c r="P3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="R3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="S3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="W3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -16186,6 +16321,44 @@
       </c>
       <c r="L63" s="14">
         <v>301810.38985605008</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="12.75">
+      <c r="A64" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="13">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="13">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="14">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="14">
+        <v>-35250.090060671617</v>
+      </c>
+      <c r="F64" s="15">
+        <v>-31842.899975831897</v>
+      </c>
+      <c r="G64" s="15">
+        <v>1316349.7340736755</v>
+      </c>
+      <c r="H64" s="15">
+        <v>1457199.1468319762</v>
+      </c>
+      <c r="I64" s="15">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J64" s="15">
+        <v>1794259.6267486978</v>
+      </c>
+      <c r="K64" s="15">
+        <v>635766.59726647404</v>
+      </c>
+      <c r="L64" s="14">
+        <v>337060.4799167217</v>
       </c>
     </row>
   </sheetData>
@@ -16204,7 +16377,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM63"/>
+  <dimension ref="A1:AM64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -16239,7 +16412,7 @@
   <sheetData>
     <row r="1" spans="1:39" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B1" s="25" t="s">
         <v>8</v>
@@ -16379,28 +16552,28 @@
       <c r="R3" s="23"/>
       <c r="S3" s="9"/>
       <c r="V3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="W3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="W3" s="16" t="s">
+      <c r="X3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="X3" s="16" t="s">
+      <c r="Y3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="Y3" s="16" t="s">
+      <c r="Z3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="Z3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="AA3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="AB3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="AC3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="AE3" s="24">
         <v>44561</v>
@@ -20364,6 +20537,71 @@
       </c>
       <c r="U63" s="11">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" ht="12.75">
+      <c r="A64" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="13">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="13">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="14">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="14">
+        <v>-35250.090060671617</v>
+      </c>
+      <c r="F64" s="15">
+        <v>-31842.899975831897</v>
+      </c>
+      <c r="G64" s="15">
+        <v>1378502.5730276722</v>
+      </c>
+      <c r="H64" s="15">
+        <v>1526002.3391391358</v>
+      </c>
+      <c r="I64" s="15">
+        <v>1222236.9259249454</v>
+      </c>
+      <c r="J64" s="15">
+        <v>1904456.8522721031</v>
+      </c>
+      <c r="K64" s="15">
+        <v>682219.92634715769</v>
+      </c>
+      <c r="L64" s="14">
+        <v>378454.51313296735</v>
+      </c>
+      <c r="M64" s="23">
+        <v>1.281999945640564</v>
+      </c>
+      <c r="N64" s="23">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="O64" s="23">
+        <v>1.1546666622161865</v>
+      </c>
+      <c r="P64" s="23">
+        <v>1.0564761956532798</v>
+      </c>
+      <c r="Q64" s="23">
+        <v>9.8190466562906753E-2</v>
+      </c>
+      <c r="R64" s="23">
+        <v>8.5721089726402591E-2</v>
+      </c>
+      <c r="S64" s="9">
+        <v>1.2858163458960388E-3</v>
+      </c>
+      <c r="T64" s="9">
+        <v>76.364301073246494</v>
+      </c>
+      <c r="U64" s="11">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -20382,7 +20620,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG63"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -20417,7 +20655,7 @@
   <sheetData>
     <row r="1" spans="1:33" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B1" s="25" t="s">
         <v>8</v>
@@ -20523,28 +20761,28 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="R3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="S3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="W3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -23415,6 +23653,50 @@
         <v>66.335527216233743</v>
       </c>
       <c r="N63" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="12.75">
+      <c r="A64" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="13">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="13">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="14">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="14">
+        <v>-35250.090060671617</v>
+      </c>
+      <c r="F64" s="15">
+        <v>-31842.899975831897</v>
+      </c>
+      <c r="G64" s="15">
+        <v>1399168.3450678764</v>
+      </c>
+      <c r="H64" s="15">
+        <v>1548879.3486496827</v>
+      </c>
+      <c r="I64" s="15">
+        <v>1226222.9374500697</v>
+      </c>
+      <c r="J64" s="15">
+        <v>1902459.1060100065</v>
+      </c>
+      <c r="K64" s="15">
+        <v>676236.16855993681</v>
+      </c>
+      <c r="L64" s="14">
+        <v>353579.75736032374</v>
+      </c>
+      <c r="M64" s="9">
+        <v>-82.62240642203966</v>
+      </c>
+      <c r="N64" s="9">
         <v>1</v>
       </c>
     </row>
@@ -23434,7 +23716,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG63"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -23469,7 +23751,7 @@
   <sheetData>
     <row r="1" spans="1:33" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
         <v>8</v>
@@ -23575,28 +23857,28 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="R3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="S3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="W3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -26467,6 +26749,50 @@
         <v>66.335527216233743</v>
       </c>
       <c r="N63" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="12.75">
+      <c r="A64" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="13">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="13">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="14">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="14">
+        <v>-314574.39222416701</v>
+      </c>
+      <c r="F64" s="15">
+        <v>-284168.3777065904</v>
+      </c>
+      <c r="G64" s="15">
+        <v>11759663.097474437</v>
+      </c>
+      <c r="H64" s="15">
+        <v>13017946.970399981</v>
+      </c>
+      <c r="I64" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J64" s="15">
+        <v>15927950.34825873</v>
+      </c>
+      <c r="K64" s="15">
+        <v>5965164.9690088201</v>
+      </c>
+      <c r="L64" s="14">
+        <v>2910003.3778587496</v>
+      </c>
+      <c r="M64" s="9">
+        <v>-82.62240642203966</v>
+      </c>
+      <c r="N64" s="9">
         <v>1</v>
       </c>
     </row>
@@ -26486,7 +26812,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI63"/>
+  <dimension ref="A1:AI64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -26521,7 +26847,7 @@
   <sheetData>
     <row r="1" spans="1:35" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
         <v>8</v>
@@ -26641,28 +26967,28 @@
         <v>1</v>
       </c>
       <c r="R3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="S3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="T3" s="16" t="s">
+      <c r="U3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="U3" s="16" t="s">
+      <c r="V3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="V3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="W3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="X3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="Y3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="AA3" s="24">
         <v>44561</v>
@@ -29893,6 +30219,56 @@
         <v>66.335527216233743</v>
       </c>
       <c r="P63" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" ht="12.75">
+      <c r="A64" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="13">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="13">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="14">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="14">
+        <v>4485200</v>
+      </c>
+      <c r="F64" s="14">
+        <v>4013151.7473958335</v>
+      </c>
+      <c r="G64" s="14">
+        <v>-351576.30531150417</v>
+      </c>
+      <c r="H64" s="15">
+        <v>-317593.77365101298</v>
+      </c>
+      <c r="I64" s="15">
+        <v>11975755.658909511</v>
+      </c>
+      <c r="J64" s="15">
+        <v>13257161.434466034</v>
+      </c>
+      <c r="K64" s="15">
+        <v>8864712.2860347666</v>
+      </c>
+      <c r="L64" s="15">
+        <v>15310756.323999755</v>
+      </c>
+      <c r="M64" s="15">
+        <v>6446044.0379649885</v>
+      </c>
+      <c r="N64" s="14">
+        <v>2053594.8895337218</v>
+      </c>
+      <c r="O64" s="9">
+        <v>-82.62240642203966</v>
+      </c>
+      <c r="P64" s="9">
         <v>1</v>
       </c>
     </row>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI)cn.xlsx
@@ -157,10 +157,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>最高价</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -171,6 +167,10 @@
   <si>
     <t>标志</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>成交量</t>
@@ -601,7 +601,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -787,6 +787,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -796,7 +799,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -981,6 +984,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -1024,7 +1030,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1210,6 +1216,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1219,7 +1228,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1405,6 +1414,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1794259.6267486978</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1803474.034715408</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1447,7 +1459,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1633,6 +1645,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1642,7 +1657,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1828,6 +1843,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>635766.59726647404</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>644981.0052331842</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1849,11 +1867,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="503908608"/>
-        <c:axId val="503914496"/>
+        <c:axId val="375884800"/>
+        <c:axId val="376420992"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="503908608"/>
+        <c:axId val="375884800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1896,14 +1914,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="503914496"/>
+        <c:crossAx val="376420992"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="503914496"/>
+        <c:axId val="376420992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1954,7 +1972,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="503908608"/>
+        <c:crossAx val="375884800"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2145,7 +2163,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2331,6 +2349,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-351576.30531150417</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-130359.36832865544</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2345,8 +2366,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="692910720"/>
-        <c:axId val="692909184"/>
+        <c:axId val="491117184"/>
+        <c:axId val="491115648"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2371,7 +2392,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2557,6 +2578,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2566,7 +2590,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2752,6 +2776,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2768,11 +2795,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="692893568"/>
-        <c:axId val="692895104"/>
+        <c:axId val="491104128"/>
+        <c:axId val="491105664"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="692893568"/>
+        <c:axId val="491104128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2815,14 +2842,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692895104"/>
+        <c:crossAx val="491105664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="692895104"/>
+        <c:axId val="491105664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2873,12 +2900,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692893568"/>
+        <c:crossAx val="491104128"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="692909184"/>
+        <c:axId val="491115648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2915,12 +2942,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692910720"/>
+        <c:crossAx val="491117184"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="692910720"/>
+        <c:axId val="491117184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2929,7 +2956,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="692909184"/>
+        <c:crossAx val="491115648"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3091,7 +3118,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3277,6 +3304,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-35250.090060671617</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-34946.17272282279</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3291,8 +3321,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="509547264"/>
-        <c:axId val="503970432"/>
+        <c:axId val="463620736"/>
+        <c:axId val="459296768"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3317,7 +3347,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3503,6 +3533,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3512,7 +3545,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3698,6 +3731,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3714,11 +3750,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="503966336"/>
-        <c:axId val="503968896"/>
+        <c:axId val="458131328"/>
+        <c:axId val="458170368"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="503966336"/>
+        <c:axId val="458131328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3761,14 +3797,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="503968896"/>
+        <c:crossAx val="458170368"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="503968896"/>
+        <c:axId val="458170368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3819,12 +3855,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="503966336"/>
+        <c:crossAx val="458131328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="503970432"/>
+        <c:axId val="459296768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3861,12 +3897,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="509547264"/>
+        <c:crossAx val="463620736"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="509547264"/>
+        <c:axId val="463620736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3875,7 +3911,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="503970432"/>
+        <c:crossAx val="459296768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4054,7 +4090,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4240,6 +4276,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4249,7 +4288,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4434,6 +4473,9 @@
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>1222236.9259249454</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
               </c:numCache>
@@ -4477,7 +4519,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4663,6 +4705,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4672,7 +4717,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4858,6 +4903,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1904456.8522721031</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1914106.3282147367</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4900,7 +4948,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5086,6 +5134,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5095,7 +5146,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5281,6 +5332,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>682219.92634715769</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>691869.40228979127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5302,11 +5356,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="569178752"/>
-        <c:axId val="692671232"/>
+        <c:axId val="494939520"/>
+        <c:axId val="494966272"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="569178752"/>
+        <c:axId val="494939520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5349,14 +5403,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692671232"/>
+        <c:crossAx val="494966272"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="692671232"/>
+        <c:axId val="494966272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5407,7 +5461,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="569178752"/>
+        <c:crossAx val="494939520"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5598,7 +5652,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5784,6 +5838,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-35250.090060671617</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-34946.17272282279</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5798,8 +5855,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="693161984"/>
-        <c:axId val="692967680"/>
+        <c:axId val="508956032"/>
+        <c:axId val="495650688"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5824,7 +5881,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6010,6 +6067,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6019,7 +6079,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -6205,6 +6265,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6221,11 +6284,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="692865664"/>
-        <c:axId val="692965760"/>
+        <c:axId val="495561344"/>
+        <c:axId val="495649152"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="692865664"/>
+        <c:axId val="495561344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6268,14 +6331,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692965760"/>
+        <c:crossAx val="495649152"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="692965760"/>
+        <c:axId val="495649152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6326,12 +6389,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692865664"/>
+        <c:crossAx val="495561344"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="692967680"/>
+        <c:axId val="495650688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6368,12 +6431,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="693161984"/>
+        <c:crossAx val="508956032"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="693161984"/>
+        <c:axId val="508956032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6382,7 +6445,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="692967680"/>
+        <c:crossAx val="495650688"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6561,7 +6624,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6747,6 +6810,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6756,7 +6822,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6941,6 +7007,9 @@
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>1226222.9374500697</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
               </c:numCache>
@@ -6984,7 +7053,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7170,6 +7239,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7179,7 +7251,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7365,6 +7437,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1902459.1060100065</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1912253.2417262525</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7407,7 +7482,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7593,6 +7668,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7602,7 +7680,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7788,6 +7866,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>676236.16855993681</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>686030.30427618278</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7809,11 +7890,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="728949888"/>
-        <c:axId val="728952832"/>
+        <c:axId val="532582784"/>
+        <c:axId val="532584704"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="728949888"/>
+        <c:axId val="532582784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7856,14 +7937,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="728952832"/>
+        <c:crossAx val="532584704"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="728952832"/>
+        <c:axId val="532584704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7914,7 +7995,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="728949888"/>
+        <c:crossAx val="532582784"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8105,7 +8186,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="63"/>
+                <c:ptCount val="64"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8291,6 +8372,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-35250.090060671617</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-34946.17272282279</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8305,8 +8389,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="730074496"/>
-        <c:axId val="730072192"/>
+        <c:axId val="533947904"/>
+        <c:axId val="533945344"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8331,7 +8415,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8517,6 +8601,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8526,7 +8613,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8712,6 +8799,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8728,11 +8818,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="730031616"/>
-        <c:axId val="730033536"/>
+        <c:axId val="532610432"/>
+        <c:axId val="533942656"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="730031616"/>
+        <c:axId val="532610432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8775,14 +8865,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="730033536"/>
+        <c:crossAx val="533942656"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="730033536"/>
+        <c:axId val="533942656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8833,12 +8923,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="730031616"/>
+        <c:crossAx val="532610432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="730072192"/>
+        <c:axId val="533945344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8875,12 +8965,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="730074496"/>
+        <c:crossAx val="533947904"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="730074496"/>
+        <c:axId val="533947904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8889,7 +8979,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="730072192"/>
+        <c:crossAx val="533945344"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9068,7 +9158,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9254,6 +9344,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9263,7 +9356,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9448,6 +9541,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -9491,7 +9587,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9677,6 +9773,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9686,7 +9785,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9872,6 +9971,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>15927950.34825873</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>16010267.631064614</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9914,7 +10016,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10100,6 +10202,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10109,7 +10214,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10295,6 +10400,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>5965164.9690088201</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6047482.2518147044</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10316,11 +10424,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="730145152"/>
-        <c:axId val="730147840"/>
+        <c:axId val="534522880"/>
+        <c:axId val="534599168"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="730145152"/>
+        <c:axId val="534522880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10363,14 +10471,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="730147840"/>
+        <c:crossAx val="534599168"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="730147840"/>
+        <c:axId val="534599168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10421,7 +10529,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="730145152"/>
+        <c:crossAx val="534522880"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10612,7 +10720,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10798,6 +10906,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>11759663.097474437</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>11482128.604656462</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10812,8 +10923,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="692485120"/>
-        <c:axId val="692483584"/>
+        <c:axId val="490310656"/>
+        <c:axId val="490309120"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10838,7 +10949,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11024,6 +11135,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11033,7 +11147,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -11219,6 +11333,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11235,11 +11352,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="691517696"/>
-        <c:axId val="692482048"/>
+        <c:axId val="490301696"/>
+        <c:axId val="490307584"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="691517696"/>
+        <c:axId val="490301696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11282,14 +11399,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692482048"/>
+        <c:crossAx val="490307584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="692482048"/>
+        <c:axId val="490307584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11340,12 +11457,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="691517696"/>
+        <c:crossAx val="490301696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="692483584"/>
+        <c:axId val="490309120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11382,12 +11499,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692485120"/>
+        <c:crossAx val="490310656"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="692485120"/>
+        <c:axId val="490310656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11396,7 +11513,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="692483584"/>
+        <c:crossAx val="490309120"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11575,7 +11692,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11761,6 +11878,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11770,7 +11890,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11955,6 +12075,9 @@
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>8864712.2860347666</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
               </c:numCache>
@@ -11998,7 +12121,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12184,6 +12307,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12193,7 +12319,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12379,6 +12505,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>15310756.323999755</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>15394586.248141063</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12421,7 +12550,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12607,6 +12736,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12616,7 +12748,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12802,6 +12934,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>6446044.0379649885</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6529873.9621062968</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12823,11 +12958,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="692680960"/>
-        <c:axId val="692707328"/>
+        <c:axId val="490912000"/>
+        <c:axId val="490921984"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="692680960"/>
+        <c:axId val="490912000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12870,14 +13005,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692707328"/>
+        <c:crossAx val="490921984"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="692707328"/>
+        <c:axId val="490921984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12928,7 +13063,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="692680960"/>
+        <c:crossAx val="490912000"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13642,7 +13777,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -16361,6 +16496,44 @@
         <v>337060.4799167217</v>
       </c>
     </row>
+    <row r="65" spans="1:12" ht="12.75">
+      <c r="A65" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="13">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="13">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="14">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="14">
+        <v>-34946.17272282279</v>
+      </c>
+      <c r="F65" s="15">
+        <v>-31369.994514880033</v>
+      </c>
+      <c r="G65" s="15">
+        <v>1284979.7395587955</v>
+      </c>
+      <c r="H65" s="15">
+        <v>1431467.3820758634</v>
+      </c>
+      <c r="I65" s="15">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J65" s="15">
+        <v>1803474.034715408</v>
+      </c>
+      <c r="K65" s="15">
+        <v>644981.0052331842</v>
+      </c>
+      <c r="L65" s="14">
+        <v>372006.65263954451</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -16377,7 +16550,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM64"/>
+  <dimension ref="A1:AM65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -16412,7 +16585,7 @@
   <sheetData>
     <row r="1" spans="1:39" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
         <v>8</v>
@@ -16448,10 +16621,10 @@
         <v>18</v>
       </c>
       <c r="M1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>4</v>
@@ -16472,7 +16645,7 @@
         <v>3</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:39" ht="14.1" customHeight="1">
@@ -20601,6 +20774,71 @@
         <v>76.364301073246494</v>
       </c>
       <c r="U64" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" ht="12.75">
+      <c r="A65" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="13">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="13">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="14">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="14">
+        <v>-34946.17272282279</v>
+      </c>
+      <c r="F65" s="15">
+        <v>-31369.994514880033</v>
+      </c>
+      <c r="G65" s="15">
+        <v>1347132.5785127922</v>
+      </c>
+      <c r="H65" s="15">
+        <v>1500705.6423589466</v>
+      </c>
+      <c r="I65" s="15">
+        <v>1222236.9259249454</v>
+      </c>
+      <c r="J65" s="15">
+        <v>1914106.3282147367</v>
+      </c>
+      <c r="K65" s="15">
+        <v>691869.40228979127</v>
+      </c>
+      <c r="L65" s="14">
+        <v>413400.68585579016</v>
+      </c>
+      <c r="M65" s="23">
+        <v>1.1759999990463257</v>
+      </c>
+      <c r="N65" s="23">
+        <v>1.093000054359436</v>
+      </c>
+      <c r="O65" s="23">
+        <v>1.1276666720708211</v>
+      </c>
+      <c r="P65" s="23">
+        <v>1.0799047677289875</v>
+      </c>
+      <c r="Q65" s="23">
+        <v>4.7761904341833583E-2</v>
+      </c>
+      <c r="R65" s="23">
+        <v>7.0020411087542242E-2</v>
+      </c>
+      <c r="S65" s="9">
+        <v>1.0503061663131336E-3</v>
+      </c>
+      <c r="T65" s="9">
+        <v>45.47426824074654</v>
+      </c>
+      <c r="U65" s="11">
         <v>1</v>
       </c>
     </row>
@@ -20620,7 +20858,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -20655,7 +20893,7 @@
   <sheetData>
     <row r="1" spans="1:33" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B1" s="25" t="s">
         <v>8</v>
@@ -20694,7 +20932,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -23697,6 +23935,50 @@
         <v>-82.62240642203966</v>
       </c>
       <c r="N64" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="12.75">
+      <c r="A65" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="13">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="13">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="14">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="14">
+        <v>-34946.17272282279</v>
+      </c>
+      <c r="F65" s="15">
+        <v>-31369.994514880033</v>
+      </c>
+      <c r="G65" s="15">
+        <v>1367798.3505529964</v>
+      </c>
+      <c r="H65" s="15">
+        <v>1523727.3116431059</v>
+      </c>
+      <c r="I65" s="15">
+        <v>1226222.9374500697</v>
+      </c>
+      <c r="J65" s="15">
+        <v>1912253.2417262525</v>
+      </c>
+      <c r="K65" s="15">
+        <v>686030.30427618278</v>
+      </c>
+      <c r="L65" s="14">
+        <v>388525.93008314655</v>
+      </c>
+      <c r="M65" s="9">
+        <v>-90.561561933820059</v>
+      </c>
+      <c r="N65" s="9">
         <v>1</v>
       </c>
     </row>
@@ -23716,7 +23998,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -23790,7 +24072,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -26793,6 +27075,50 @@
         <v>-82.62240642203966</v>
       </c>
       <c r="N64" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="12.75">
+      <c r="A65" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="13">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="13">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="14">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="14">
+        <v>-309173.41467680095</v>
+      </c>
+      <c r="F65" s="15">
+        <v>-277534.492817975</v>
+      </c>
+      <c r="G65" s="15">
+        <v>11482128.604656462</v>
+      </c>
+      <c r="H65" s="15">
+        <v>12791090.838529063</v>
+      </c>
+      <c r="I65" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J65" s="15">
+        <v>16010267.631064614</v>
+      </c>
+      <c r="K65" s="15">
+        <v>6047482.2518147044</v>
+      </c>
+      <c r="L65" s="14">
+        <v>3219176.7925355504</v>
+      </c>
+      <c r="M65" s="9">
+        <v>-90.561561933820059</v>
+      </c>
+      <c r="N65" s="9">
         <v>1</v>
       </c>
     </row>
@@ -26812,7 +27138,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI64"/>
+  <dimension ref="A1:AI65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -26892,7 +27218,7 @@
         <v>0</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="14.1" customHeight="1">
@@ -30269,6 +30595,56 @@
         <v>-82.62240642203966</v>
       </c>
       <c r="P64" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="12.75">
+      <c r="A65" s="12">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="13">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="13">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="14">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="14">
+        <v>1687200</v>
+      </c>
+      <c r="F65" s="14">
+        <v>4001533.5447742641</v>
+      </c>
+      <c r="G65" s="14">
+        <v>-130359.36832865544</v>
+      </c>
+      <c r="H65" s="15">
+        <v>-117019.18553050711</v>
+      </c>
+      <c r="I65" s="15">
+        <v>11858736.473379003</v>
+      </c>
+      <c r="J65" s="15">
+        <v>13210631.990278685</v>
+      </c>
+      <c r="K65" s="15">
+        <v>8864712.2860347666</v>
+      </c>
+      <c r="L65" s="15">
+        <v>15394586.248141063</v>
+      </c>
+      <c r="M65" s="15">
+        <v>6529873.9621062968</v>
+      </c>
+      <c r="N65" s="14">
+        <v>2183954.2578623774</v>
+      </c>
+      <c r="O65" s="9">
+        <v>-90.561561933820059</v>
+      </c>
+      <c r="P65" s="9">
         <v>1</v>
       </c>
     </row>
